--- a/final_data_pipeline/output/311313longform.xlsx
+++ b/final_data_pipeline/output/311313longform.xlsx
@@ -1089,7 +1089,7 @@
         <v>171</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -1175,7 +1175,7 @@
         <v>171</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1267,7 +1267,7 @@
         <v>171</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1356,7 +1356,7 @@
         <v>171</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1439,7 +1439,7 @@
         <v>171</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1522,7 +1522,7 @@
         <v>171</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1611,7 +1611,7 @@
         <v>171</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1700,7 +1700,7 @@
         <v>171</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1789,7 +1789,7 @@
         <v>171</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1878,7 +1878,7 @@
         <v>171</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1961,7 +1961,7 @@
         <v>171</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -2044,7 +2044,7 @@
         <v>171</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -2133,7 +2133,7 @@
         <v>171</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2225,7 +2225,7 @@
         <v>171</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2317,7 +2317,7 @@
         <v>171</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2403,7 +2403,7 @@
         <v>171</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2489,7 +2489,7 @@
         <v>171</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2581,7 +2581,7 @@
         <v>171</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2670,7 +2670,7 @@
         <v>171</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2753,7 +2753,7 @@
         <v>171</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2836,7 +2836,7 @@
         <v>171</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2925,7 +2925,7 @@
         <v>171</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -3014,7 +3014,7 @@
         <v>171</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -3106,7 +3106,7 @@
         <v>171</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -3198,7 +3198,7 @@
         <v>171</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB26">
         <v>8000</v>
@@ -3293,7 +3293,7 @@
         <v>171</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB27">
         <v>8000</v>
@@ -3382,7 +3382,7 @@
         <v>172</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB28">
         <v>8000</v>
@@ -3465,7 +3465,7 @@
         <v>172</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB29">
         <v>8000</v>
@@ -3548,7 +3548,7 @@
         <v>172</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB30">
         <v>8000</v>
@@ -3637,7 +3637,7 @@
         <v>172</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB31">
         <v>8000</v>
@@ -3726,7 +3726,7 @@
         <v>172</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -5464,7 +5464,7 @@
         <v>171</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5547,7 +5547,7 @@
         <v>171</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5630,7 +5630,7 @@
         <v>171</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5713,7 +5713,7 @@
         <v>171</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5799,7 +5799,7 @@
         <v>171</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -5885,7 +5885,7 @@
         <v>171</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -5968,7 +5968,7 @@
         <v>171</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -6054,7 +6054,7 @@
         <v>171</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6140,7 +6140,7 @@
         <v>171</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6223,7 +6223,7 @@
         <v>171</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6306,7 +6306,7 @@
         <v>172</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6389,7 +6389,7 @@
         <v>172</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6472,7 +6472,7 @@
         <v>171</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6555,7 +6555,7 @@
         <v>171</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6638,7 +6638,7 @@
         <v>171</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6724,7 +6724,7 @@
         <v>171</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -6810,7 +6810,7 @@
         <v>171</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -6896,7 +6896,7 @@
         <v>171</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -6979,7 +6979,7 @@
         <v>171</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7062,7 +7062,7 @@
         <v>171</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7145,7 +7145,7 @@
         <v>171</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7228,7 +7228,7 @@
         <v>171</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7311,7 +7311,7 @@
         <v>172</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7394,7 +7394,7 @@
         <v>172</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7480,7 +7480,7 @@
         <v>171</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>17.72453703703706</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7563,7 +7563,7 @@
         <v>171</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7652,7 +7652,7 @@
         <v>171</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>172</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7824,7 +7824,7 @@
         <v>172</v>
       </c>
       <c r="AA80">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB80">
         <v>8000</v>
@@ -7907,7 +7907,7 @@
         <v>171</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -7996,7 +7996,7 @@
         <v>171</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -8079,7 +8079,7 @@
         <v>171</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -8162,7 +8162,7 @@
         <v>172</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8248,7 +8248,7 @@
         <v>171</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8340,7 +8340,7 @@
         <v>171</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -8426,7 +8426,7 @@
         <v>171</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8509,7 +8509,7 @@
         <v>171</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8604,7 +8604,7 @@
         <v>171</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -8684,7 +8684,7 @@
         <v>18279.05718989691</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8767,7 +8767,7 @@
         <v>171</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -8856,7 +8856,7 @@
         <v>171</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -8939,7 +8939,7 @@
         <v>171</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9025,7 +9025,7 @@
         <v>171</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9117,7 +9117,7 @@
         <v>171</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9203,7 +9203,7 @@
         <v>171</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9292,7 +9292,7 @@
         <v>171</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9375,7 +9375,7 @@
         <v>171</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9464,7 +9464,7 @@
         <v>171</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9553,7 +9553,7 @@
         <v>171</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9636,7 +9636,7 @@
         <v>171</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9725,7 +9725,7 @@
         <v>171</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9817,7 +9817,7 @@
         <v>171</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -9900,7 +9900,7 @@
         <v>172</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -9989,7 +9989,7 @@
         <v>172</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10078,7 +10078,7 @@
         <v>172</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -10170,7 +10170,7 @@
         <v>171</v>
       </c>
       <c r="AA107">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB107">
         <v>8000</v>
@@ -10256,7 +10256,7 @@
         <v>171</v>
       </c>
       <c r="AA108">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB108">
         <v>8000</v>
@@ -10348,7 +10348,7 @@
         <v>171</v>
       </c>
       <c r="AA109">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB109">
         <v>8000</v>
@@ -10434,7 +10434,7 @@
         <v>171</v>
       </c>
       <c r="AA110">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB110">
         <v>8000</v>
@@ -10526,7 +10526,7 @@
         <v>171</v>
       </c>
       <c r="AA111">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB111">
         <v>8000</v>
@@ -10621,7 +10621,7 @@
         <v>171</v>
       </c>
       <c r="AA112">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB112">
         <v>8000</v>
@@ -10710,7 +10710,7 @@
         <v>171</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -10793,7 +10793,7 @@
         <v>171</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -10885,7 +10885,7 @@
         <v>171</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -10977,7 +10977,7 @@
         <v>171</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11063,7 +11063,7 @@
         <v>171</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11152,7 +11152,7 @@
         <v>171</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11238,7 +11238,7 @@
         <v>171</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11321,7 +11321,7 @@
         <v>171</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11407,7 +11407,7 @@
         <v>171</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -11493,7 +11493,7 @@
         <v>171</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -11576,7 +11576,7 @@
         <v>171</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -11662,7 +11662,7 @@
         <v>171</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -11748,7 +11748,7 @@
         <v>171</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -11831,7 +11831,7 @@
         <v>171</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -11914,7 +11914,7 @@
         <v>171</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -11997,7 +11997,7 @@
         <v>171</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -12080,7 +12080,7 @@
         <v>171</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -12163,7 +12163,7 @@
         <v>171</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -12249,7 +12249,7 @@
         <v>171</v>
       </c>
       <c r="AA131">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB131">
         <v>8000</v>
@@ -12335,7 +12335,7 @@
         <v>171</v>
       </c>
       <c r="AA132">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB132">
         <v>8000</v>
@@ -12421,7 +12421,7 @@
         <v>171</v>
       </c>
       <c r="AA133">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB133">
         <v>8000</v>
@@ -12504,7 +12504,7 @@
         <v>172</v>
       </c>
       <c r="AA134">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB134">
         <v>8000</v>
@@ -12587,7 +12587,7 @@
         <v>172</v>
       </c>
       <c r="AA135">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB135">
         <v>8000</v>
@@ -12670,7 +12670,7 @@
         <v>171</v>
       </c>
       <c r="AA136">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB136">
         <v>8000</v>
@@ -12753,7 +12753,7 @@
         <v>171</v>
       </c>
       <c r="AA137">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB137">
         <v>8000</v>
@@ -12836,7 +12836,7 @@
         <v>172</v>
       </c>
       <c r="AA138">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB138">
         <v>8000</v>
@@ -12922,7 +12922,7 @@
         <v>171</v>
       </c>
       <c r="AA139">
-        <v>10</v>
+        <v>-3.083333333333334</v>
       </c>
       <c r="AB139">
         <v>8000</v>
@@ -13008,7 +13008,7 @@
         <v>171</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -13094,7 +13094,7 @@
         <v>171</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -13180,7 +13180,7 @@
         <v>171</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -13263,7 +13263,7 @@
         <v>171</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -13346,7 +13346,7 @@
         <v>171</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -13429,7 +13429,7 @@
         <v>171</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -13515,7 +13515,7 @@
         <v>171</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -13598,7 +13598,7 @@
         <v>171</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -13684,7 +13684,7 @@
         <v>171</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -13767,7 +13767,7 @@
         <v>172</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -13850,7 +13850,7 @@
         <v>172</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -13933,7 +13933,7 @@
         <v>171</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -14016,7 +14016,7 @@
         <v>171</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -14102,7 +14102,7 @@
         <v>171</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -14185,7 +14185,7 @@
         <v>172</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB154">
         <v>8000</v>
@@ -14268,7 +14268,7 @@
         <v>172</v>
       </c>
       <c r="AA155">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB155">
         <v>8000</v>
@@ -14354,7 +14354,7 @@
         <v>171</v>
       </c>
       <c r="AA156">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB156">
         <v>8000</v>
@@ -14440,7 +14440,7 @@
         <v>171</v>
       </c>
       <c r="AA157">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB157">
         <v>8000</v>
@@ -14523,7 +14523,7 @@
         <v>171</v>
       </c>
       <c r="AA158">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB158">
         <v>8000</v>
@@ -14606,7 +14606,7 @@
         <v>171</v>
       </c>
       <c r="AA159">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB159">
         <v>8000</v>
@@ -14692,7 +14692,7 @@
         <v>171</v>
       </c>
       <c r="AA160">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB160">
         <v>8000</v>
@@ -14778,7 +14778,7 @@
         <v>171</v>
       </c>
       <c r="AA161">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB161">
         <v>8000</v>
@@ -14861,7 +14861,7 @@
         <v>171</v>
       </c>
       <c r="AA162">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB162">
         <v>8000</v>
@@ -14944,7 +14944,7 @@
         <v>171</v>
       </c>
       <c r="AA163">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB163">
         <v>8000</v>
@@ -15027,7 +15027,7 @@
         <v>171</v>
       </c>
       <c r="AA164">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB164">
         <v>8000</v>
@@ -15110,7 +15110,7 @@
         <v>171</v>
       </c>
       <c r="AA165">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB165">
         <v>8000</v>
@@ -15196,7 +15196,7 @@
         <v>171</v>
       </c>
       <c r="AA166">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB166">
         <v>8000</v>
@@ -15282,7 +15282,7 @@
         <v>171</v>
       </c>
       <c r="AA167">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB167">
         <v>8000</v>
@@ -15374,7 +15374,7 @@
         <v>171</v>
       </c>
       <c r="AA168">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB168">
         <v>8000</v>
@@ -15466,7 +15466,7 @@
         <v>171</v>
       </c>
       <c r="AA169">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB169">
         <v>8000</v>
@@ -15552,7 +15552,7 @@
         <v>171</v>
       </c>
       <c r="AA170">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB170">
         <v>8000</v>
@@ -15638,7 +15638,7 @@
         <v>171</v>
       </c>
       <c r="AA171">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB171">
         <v>8000</v>
@@ -15724,7 +15724,7 @@
         <v>171</v>
       </c>
       <c r="AA172">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB172">
         <v>8000</v>
@@ -15810,7 +15810,7 @@
         <v>171</v>
       </c>
       <c r="AA173">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB173">
         <v>8000</v>
@@ -15896,7 +15896,7 @@
         <v>171</v>
       </c>
       <c r="AA174">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB174">
         <v>8000</v>
@@ -15982,7 +15982,7 @@
         <v>171</v>
       </c>
       <c r="AA175">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB175">
         <v>8000</v>
@@ -16068,7 +16068,7 @@
         <v>171</v>
       </c>
       <c r="AA176">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB176">
         <v>8000</v>
@@ -16154,7 +16154,7 @@
         <v>171</v>
       </c>
       <c r="AA177">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB177">
         <v>8000</v>
@@ -16240,7 +16240,7 @@
         <v>171</v>
       </c>
       <c r="AA178">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB178">
         <v>8000</v>
@@ -16332,7 +16332,7 @@
         <v>171</v>
       </c>
       <c r="AA179">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB179">
         <v>8000</v>
@@ -16424,7 +16424,7 @@
         <v>171</v>
       </c>
       <c r="AA180">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB180">
         <v>8000</v>
@@ -16510,7 +16510,7 @@
         <v>171</v>
       </c>
       <c r="AA181">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB181">
         <v>8000</v>
@@ -16596,7 +16596,7 @@
         <v>171</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -16682,7 +16682,7 @@
         <v>171</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -16768,7 +16768,7 @@
         <v>171</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -16854,7 +16854,7 @@
         <v>171</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB185">
         <v>8000</v>
@@ -16940,7 +16940,7 @@
         <v>171</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB186">
         <v>8000</v>
@@ -17026,7 +17026,7 @@
         <v>171</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB187">
         <v>8000</v>
@@ -17112,7 +17112,7 @@
         <v>171</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB188">
         <v>8000</v>
@@ -17198,7 +17198,7 @@
         <v>171</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB189">
         <v>8000</v>
@@ -17284,7 +17284,7 @@
         <v>171</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -17370,7 +17370,7 @@
         <v>171</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -17456,7 +17456,7 @@
         <v>171</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -17539,7 +17539,7 @@
         <v>172</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -17622,7 +17622,7 @@
         <v>172</v>
       </c>
       <c r="AA194">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB194">
         <v>8000</v>
@@ -17705,7 +17705,7 @@
         <v>172</v>
       </c>
       <c r="AA195">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB195">
         <v>8000</v>
@@ -17788,7 +17788,7 @@
         <v>172</v>
       </c>
       <c r="AA196">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB196">
         <v>8000</v>
@@ -17880,7 +17880,7 @@
         <v>171</v>
       </c>
       <c r="AA197">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB197">
         <v>8000</v>
@@ -17972,7 +17972,7 @@
         <v>171</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB198">
         <v>8000</v>
@@ -18058,7 +18058,7 @@
         <v>171</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB199">
         <v>8000</v>
@@ -18144,7 +18144,7 @@
         <v>171</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB200">
         <v>8000</v>
@@ -18230,7 +18230,7 @@
         <v>171</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB201">
         <v>8000</v>
@@ -18313,7 +18313,7 @@
         <v>172</v>
       </c>
       <c r="AA202">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB202">
         <v>8000</v>
@@ -18399,7 +18399,7 @@
         <v>171</v>
       </c>
       <c r="AA203">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB203">
         <v>8000</v>
@@ -18482,7 +18482,7 @@
         <v>171</v>
       </c>
       <c r="AA204">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB204">
         <v>8000</v>
@@ -18565,7 +18565,7 @@
         <v>171</v>
       </c>
       <c r="AA205">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB205">
         <v>8000</v>
@@ -18648,7 +18648,7 @@
         <v>171</v>
       </c>
       <c r="AA206">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB206">
         <v>8000</v>
@@ -18731,7 +18731,7 @@
         <v>171</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB207">
         <v>8000</v>
@@ -18817,7 +18817,7 @@
         <v>171</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -18900,7 +18900,7 @@
         <v>171</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -18983,7 +18983,7 @@
         <v>171</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -19072,7 +19072,7 @@
         <v>171</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -19161,7 +19161,7 @@
         <v>171</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -19244,7 +19244,7 @@
         <v>171</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -19327,7 +19327,7 @@
         <v>171</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB214">
         <v>8000</v>
@@ -19410,7 +19410,7 @@
         <v>171</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB215">
         <v>8000</v>
@@ -19493,7 +19493,7 @@
         <v>171</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB216">
         <v>8000</v>
@@ -19576,7 +19576,7 @@
         <v>171</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB217">
         <v>8000</v>
@@ -19659,7 +19659,7 @@
         <v>171</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB218">
         <v>8000</v>
@@ -19748,7 +19748,7 @@
         <v>171</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB219">
         <v>8000</v>
@@ -19837,7 +19837,7 @@
         <v>171</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -19920,7 +19920,7 @@
         <v>171</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -20003,7 +20003,7 @@
         <v>171</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB222">
         <v>8000</v>
@@ -20086,7 +20086,7 @@
         <v>171</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB223">
         <v>8000</v>
@@ -20169,7 +20169,7 @@
         <v>171</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB224">
         <v>8000</v>
@@ -20252,7 +20252,7 @@
         <v>171</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB225">
         <v>8000</v>
@@ -20335,7 +20335,7 @@
         <v>171</v>
       </c>
       <c r="AA226">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB226">
         <v>8000</v>
@@ -20418,7 +20418,7 @@
         <v>171</v>
       </c>
       <c r="AA227">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB227">
         <v>8000</v>
@@ -20507,7 +20507,7 @@
         <v>171</v>
       </c>
       <c r="AA228">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB228">
         <v>8000</v>
@@ -20596,7 +20596,7 @@
         <v>171</v>
       </c>
       <c r="AA229">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB229">
         <v>8000</v>
@@ -20679,7 +20679,7 @@
         <v>171</v>
       </c>
       <c r="AA230">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB230">
         <v>8000</v>
@@ -20762,7 +20762,7 @@
         <v>171</v>
       </c>
       <c r="AA231">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB231">
         <v>8000</v>
@@ -20845,7 +20845,7 @@
         <v>171</v>
       </c>
       <c r="AA232">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB232">
         <v>8000</v>
@@ -20928,7 +20928,7 @@
         <v>171</v>
       </c>
       <c r="AA233">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB233">
         <v>8000</v>
@@ -21011,7 +21011,7 @@
         <v>171</v>
       </c>
       <c r="AA234">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB234">
         <v>8000</v>
@@ -21094,7 +21094,7 @@
         <v>171</v>
       </c>
       <c r="AA235">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB235">
         <v>8000</v>
@@ -21177,7 +21177,7 @@
         <v>171</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB236">
         <v>8000</v>
@@ -21260,7 +21260,7 @@
         <v>171</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB237">
         <v>8000</v>
@@ -21343,7 +21343,7 @@
         <v>171</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -21426,7 +21426,7 @@
         <v>172</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -21515,7 +21515,7 @@
         <v>172</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -21604,7 +21604,7 @@
         <v>172</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -21687,7 +21687,7 @@
         <v>172</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -21770,7 +21770,7 @@
         <v>172</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -21853,7 +21853,7 @@
         <v>172</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -21933,7 +21933,7 @@
         <v>167.0191129130019</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -22013,7 +22013,7 @@
         <v>515.9000522871675</v>
       </c>
       <c r="AA246">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB246">
         <v>8000</v>
@@ -22099,7 +22099,7 @@
         <v>171</v>
       </c>
       <c r="AA247">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB247">
         <v>8000</v>
@@ -22185,7 +22185,7 @@
         <v>171</v>
       </c>
       <c r="AA248">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB248">
         <v>8000</v>
@@ -22271,7 +22271,7 @@
         <v>171</v>
       </c>
       <c r="AA249">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB249">
         <v>8000</v>
@@ -22357,7 +22357,7 @@
         <v>171</v>
       </c>
       <c r="AA250">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB250">
         <v>8000</v>
@@ -22440,7 +22440,7 @@
         <v>172</v>
       </c>
       <c r="AA251">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB251">
         <v>8000</v>
@@ -22523,7 +22523,7 @@
         <v>171</v>
       </c>
       <c r="AA252">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB252">
         <v>8000</v>
@@ -22606,7 +22606,7 @@
         <v>171</v>
       </c>
       <c r="AA253">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB253">
         <v>8000</v>
@@ -29967,7 +29967,7 @@
         <v>171</v>
       </c>
       <c r="AA338">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB338">
         <v>8000</v>
@@ -30056,7 +30056,7 @@
         <v>172</v>
       </c>
       <c r="AA339">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB339">
         <v>8000</v>
@@ -30145,7 +30145,7 @@
         <v>171</v>
       </c>
       <c r="AA340">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB340">
         <v>8000</v>
@@ -30228,7 +30228,7 @@
         <v>171</v>
       </c>
       <c r="AA341">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB341">
         <v>8000</v>
@@ -30311,7 +30311,7 @@
         <v>171</v>
       </c>
       <c r="AA342">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB342">
         <v>8000</v>
@@ -30400,7 +30400,7 @@
         <v>171</v>
       </c>
       <c r="AA343">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB343">
         <v>8000</v>
@@ -30489,7 +30489,7 @@
         <v>172</v>
       </c>
       <c r="AA344">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB344">
         <v>8000</v>
@@ -30572,7 +30572,7 @@
         <v>172</v>
       </c>
       <c r="AA345">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB345">
         <v>8000</v>
@@ -30661,7 +30661,7 @@
         <v>171</v>
       </c>
       <c r="AA346">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB346">
         <v>8000</v>
@@ -30750,7 +30750,7 @@
         <v>171</v>
       </c>
       <c r="AA347">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB347">
         <v>8000</v>
@@ -30833,7 +30833,7 @@
         <v>171</v>
       </c>
       <c r="AA348">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB348">
         <v>8000</v>
@@ -30916,7 +30916,7 @@
         <v>171</v>
       </c>
       <c r="AA349">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB349">
         <v>8000</v>
@@ -31005,7 +31005,7 @@
         <v>171</v>
       </c>
       <c r="AA350">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB350">
         <v>8000</v>
@@ -31088,7 +31088,7 @@
         <v>172</v>
       </c>
       <c r="AA351">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB351">
         <v>8000</v>
@@ -31180,7 +31180,7 @@
         <v>171</v>
       </c>
       <c r="AA352">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB352">
         <v>8000</v>
@@ -31263,7 +31263,7 @@
         <v>171</v>
       </c>
       <c r="AA353">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB353">
         <v>8000</v>
@@ -31355,7 +31355,7 @@
         <v>171</v>
       </c>
       <c r="AA354">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB354">
         <v>8000</v>
@@ -31441,7 +31441,7 @@
         <v>171</v>
       </c>
       <c r="AA355">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB355">
         <v>8000</v>
@@ -31527,7 +31527,7 @@
         <v>171</v>
       </c>
       <c r="AA356">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB356">
         <v>8000</v>
@@ -31610,7 +31610,7 @@
         <v>171</v>
       </c>
       <c r="AA357">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB357">
         <v>8000</v>
@@ -31702,7 +31702,7 @@
         <v>171</v>
       </c>
       <c r="AA358">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB358">
         <v>8000</v>
@@ -31794,7 +31794,7 @@
         <v>171</v>
       </c>
       <c r="AA359">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB359">
         <v>8000</v>
@@ -31880,7 +31880,7 @@
         <v>171</v>
       </c>
       <c r="AA360">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB360">
         <v>8000</v>
@@ -31966,7 +31966,7 @@
         <v>171</v>
       </c>
       <c r="AA361">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB361">
         <v>8000</v>
@@ -32058,7 +32058,7 @@
         <v>171</v>
       </c>
       <c r="AA362">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB362">
         <v>8000</v>
@@ -32150,7 +32150,7 @@
         <v>171</v>
       </c>
       <c r="AA363">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB363">
         <v>8000</v>
@@ -32245,7 +32245,7 @@
         <v>171</v>
       </c>
       <c r="AA364">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB364">
         <v>8000</v>
@@ -32331,7 +32331,7 @@
         <v>171</v>
       </c>
       <c r="AA365">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB365">
         <v>8000</v>
@@ -32417,7 +32417,7 @@
         <v>171</v>
       </c>
       <c r="AA366">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AB366">
         <v>8000</v>
@@ -37079,7 +37079,7 @@
         <v>171</v>
       </c>
       <c r="AA420">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB420">
         <v>8000</v>
@@ -37168,7 +37168,7 @@
         <v>171</v>
       </c>
       <c r="AA421">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB421">
         <v>8000</v>
@@ -37257,7 +37257,7 @@
         <v>171</v>
       </c>
       <c r="AA422">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB422">
         <v>8000</v>
@@ -37340,7 +37340,7 @@
         <v>171</v>
       </c>
       <c r="AA423">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB423">
         <v>8000</v>
@@ -37432,7 +37432,7 @@
         <v>171</v>
       </c>
       <c r="AA424">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB424">
         <v>8000</v>
@@ -37515,7 +37515,7 @@
         <v>171</v>
       </c>
       <c r="AA425">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB425">
         <v>8000</v>
@@ -37604,7 +37604,7 @@
         <v>171</v>
       </c>
       <c r="AA426">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB426">
         <v>8000</v>
@@ -37693,7 +37693,7 @@
         <v>171</v>
       </c>
       <c r="AA427">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB427">
         <v>8000</v>
@@ -37776,7 +37776,7 @@
         <v>171</v>
       </c>
       <c r="AA428">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB428">
         <v>8000</v>
@@ -37865,7 +37865,7 @@
         <v>171</v>
       </c>
       <c r="AA429">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB429">
         <v>8000</v>
@@ -37954,7 +37954,7 @@
         <v>171</v>
       </c>
       <c r="AA430">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB430">
         <v>8000</v>
@@ -38049,7 +38049,7 @@
         <v>171</v>
       </c>
       <c r="AA431">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB431">
         <v>8000</v>
@@ -38138,7 +38138,7 @@
         <v>172</v>
       </c>
       <c r="AA432">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB432">
         <v>8000</v>
@@ -38221,7 +38221,7 @@
         <v>172</v>
       </c>
       <c r="AA433">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB433">
         <v>8000</v>
@@ -38304,7 +38304,7 @@
         <v>171</v>
       </c>
       <c r="AA434">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB434">
         <v>8000</v>
@@ -38393,7 +38393,7 @@
         <v>171</v>
       </c>
       <c r="AA435">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB435">
         <v>8000</v>
@@ -38485,7 +38485,7 @@
         <v>171</v>
       </c>
       <c r="AA436">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB436">
         <v>8000</v>
@@ -38571,7 +38571,7 @@
         <v>171</v>
       </c>
       <c r="AA437">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB437">
         <v>8000</v>
@@ -38663,7 +38663,7 @@
         <v>171</v>
       </c>
       <c r="AA438">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB438">
         <v>8000</v>
@@ -38749,7 +38749,7 @@
         <v>171</v>
       </c>
       <c r="AA439">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB439">
         <v>8000</v>
@@ -38841,7 +38841,7 @@
         <v>171</v>
       </c>
       <c r="AA440">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB440">
         <v>8000</v>
@@ -38933,7 +38933,7 @@
         <v>171</v>
       </c>
       <c r="AA441">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB441">
         <v>8000</v>
@@ -39019,7 +39019,7 @@
         <v>171</v>
       </c>
       <c r="AA442">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB442">
         <v>8000</v>
@@ -39111,7 +39111,7 @@
         <v>171</v>
       </c>
       <c r="AA443">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB443">
         <v>8000</v>
@@ -39197,7 +39197,7 @@
         <v>171</v>
       </c>
       <c r="AA444">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB444">
         <v>8000</v>
@@ -39286,7 +39286,7 @@
         <v>171</v>
       </c>
       <c r="AA445">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB445">
         <v>8000</v>
@@ -39375,7 +39375,7 @@
         <v>171</v>
       </c>
       <c r="AA446">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB446">
         <v>8000</v>
@@ -39464,7 +39464,7 @@
         <v>172</v>
       </c>
       <c r="AA447">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB447">
         <v>8000</v>
@@ -39547,7 +39547,7 @@
         <v>172</v>
       </c>
       <c r="AA448">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB448">
         <v>8000</v>
@@ -39636,7 +39636,7 @@
         <v>172</v>
       </c>
       <c r="AA449">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB449">
         <v>8000</v>
@@ -39716,7 +39716,7 @@
         <v>432.2405843487079</v>
       </c>
       <c r="AA450">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB450">
         <v>8000</v>
@@ -39799,7 +39799,7 @@
         <v>171</v>
       </c>
       <c r="AA451">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB451">
         <v>8000</v>
@@ -39879,7 +39879,7 @@
         <v>99.13392508384629</v>
       </c>
       <c r="AA452">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB452">
         <v>8000</v>
@@ -39965,7 +39965,7 @@
         <v>171</v>
       </c>
       <c r="AA453">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB453">
         <v>8000</v>
@@ -40048,7 +40048,7 @@
         <v>172</v>
       </c>
       <c r="AA454">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB454">
         <v>8000</v>
@@ -40131,7 +40131,7 @@
         <v>172</v>
       </c>
       <c r="AA455">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB455">
         <v>8000</v>
@@ -40214,7 +40214,7 @@
         <v>172</v>
       </c>
       <c r="AA456">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB456">
         <v>8000</v>
@@ -40297,7 +40297,7 @@
         <v>171</v>
       </c>
       <c r="AA457">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB457">
         <v>8000</v>
@@ -40380,7 +40380,7 @@
         <v>171</v>
       </c>
       <c r="AA458">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB458">
         <v>8000</v>
@@ -40466,7 +40466,7 @@
         <v>171</v>
       </c>
       <c r="AA459">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB459">
         <v>8000</v>
@@ -40552,7 +40552,7 @@
         <v>171</v>
       </c>
       <c r="AA460">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB460">
         <v>8000</v>
@@ -40635,7 +40635,7 @@
         <v>171</v>
       </c>
       <c r="AA461">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB461">
         <v>8000</v>
@@ -40718,7 +40718,7 @@
         <v>171</v>
       </c>
       <c r="AA462">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB462">
         <v>8000</v>
@@ -40801,7 +40801,7 @@
         <v>171</v>
       </c>
       <c r="AA463">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB463">
         <v>8000</v>
@@ -40884,7 +40884,7 @@
         <v>171</v>
       </c>
       <c r="AA464">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB464">
         <v>8000</v>
@@ -40970,7 +40970,7 @@
         <v>171</v>
       </c>
       <c r="AA465">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB465">
         <v>8000</v>
@@ -41056,7 +41056,7 @@
         <v>171</v>
       </c>
       <c r="AA466">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB466">
         <v>8000</v>
@@ -41139,7 +41139,7 @@
         <v>171</v>
       </c>
       <c r="AA467">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB467">
         <v>8000</v>
@@ -41225,7 +41225,7 @@
         <v>171</v>
       </c>
       <c r="AA468">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB468">
         <v>8000</v>
@@ -41320,7 +41320,7 @@
         <v>171</v>
       </c>
       <c r="AA469">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB469">
         <v>8000</v>
@@ -41403,7 +41403,7 @@
         <v>171</v>
       </c>
       <c r="AA470">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB470">
         <v>8000</v>
@@ -41486,7 +41486,7 @@
         <v>171</v>
       </c>
       <c r="AA471">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB471">
         <v>8000</v>
@@ -41581,7 +41581,7 @@
         <v>171</v>
       </c>
       <c r="AA472">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB472">
         <v>8000</v>
@@ -47554,7 +47554,7 @@
         <v>172</v>
       </c>
       <c r="AA541">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB541">
         <v>8000</v>
@@ -47640,7 +47640,7 @@
         <v>171</v>
       </c>
       <c r="AA542">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB542">
         <v>8000</v>
@@ -47729,7 +47729,7 @@
         <v>171</v>
       </c>
       <c r="AA543">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB543">
         <v>8000</v>
@@ -47812,7 +47812,7 @@
         <v>171</v>
       </c>
       <c r="AA544">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB544">
         <v>8000</v>
@@ -47895,7 +47895,7 @@
         <v>171</v>
       </c>
       <c r="AA545">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB545">
         <v>8000</v>
@@ -47978,7 +47978,7 @@
         <v>171</v>
       </c>
       <c r="AA546">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB546">
         <v>8000</v>
@@ -48061,7 +48061,7 @@
         <v>171</v>
       </c>
       <c r="AA547">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB547">
         <v>8000</v>
@@ -48144,7 +48144,7 @@
         <v>171</v>
       </c>
       <c r="AA548">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB548">
         <v>8000</v>
@@ -48230,7 +48230,7 @@
         <v>171</v>
       </c>
       <c r="AA549">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB549">
         <v>8000</v>
@@ -48319,7 +48319,7 @@
         <v>171</v>
       </c>
       <c r="AA550">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB550">
         <v>8000</v>
@@ -48408,7 +48408,7 @@
         <v>171</v>
       </c>
       <c r="AA551">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB551">
         <v>8000</v>
@@ -48497,7 +48497,7 @@
         <v>171</v>
       </c>
       <c r="AA552">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB552">
         <v>8000</v>
@@ -48586,7 +48586,7 @@
         <v>171</v>
       </c>
       <c r="AA553">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB553">
         <v>8000</v>
@@ -48675,7 +48675,7 @@
         <v>171</v>
       </c>
       <c r="AA554">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB554">
         <v>8000</v>
@@ -48758,7 +48758,7 @@
         <v>171</v>
       </c>
       <c r="AA555">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB555">
         <v>8000</v>
@@ -48841,7 +48841,7 @@
         <v>171</v>
       </c>
       <c r="AA556">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB556">
         <v>8000</v>
@@ -48924,7 +48924,7 @@
         <v>171</v>
       </c>
       <c r="AA557">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB557">
         <v>8000</v>
@@ -49007,7 +49007,7 @@
         <v>171</v>
       </c>
       <c r="AA558">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB558">
         <v>8000</v>
@@ -49090,7 +49090,7 @@
         <v>171</v>
       </c>
       <c r="AA559">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB559">
         <v>8000</v>
@@ -49173,7 +49173,7 @@
         <v>171</v>
       </c>
       <c r="AA560">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB560">
         <v>8000</v>
@@ -49256,7 +49256,7 @@
         <v>171</v>
       </c>
       <c r="AA561">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB561">
         <v>8000</v>
@@ -49339,7 +49339,7 @@
         <v>171</v>
       </c>
       <c r="AA562">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB562">
         <v>8000</v>
@@ -49428,7 +49428,7 @@
         <v>171</v>
       </c>
       <c r="AA563">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB563">
         <v>8000</v>
@@ -49517,7 +49517,7 @@
         <v>171</v>
       </c>
       <c r="AA564">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB564">
         <v>8000</v>
@@ -49606,7 +49606,7 @@
         <v>171</v>
       </c>
       <c r="AA565">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB565">
         <v>8000</v>
@@ -49689,7 +49689,7 @@
         <v>171</v>
       </c>
       <c r="AA566">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB566">
         <v>8000</v>
@@ -49772,7 +49772,7 @@
         <v>171</v>
       </c>
       <c r="AA567">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB567">
         <v>8000</v>
@@ -49858,7 +49858,7 @@
         <v>171</v>
       </c>
       <c r="AA568">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB568">
         <v>8000</v>
@@ -49944,7 +49944,7 @@
         <v>171</v>
       </c>
       <c r="AA569">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB569">
         <v>8000</v>
@@ -50030,7 +50030,7 @@
         <v>171</v>
       </c>
       <c r="AA570">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB570">
         <v>8000</v>
@@ -50116,7 +50116,7 @@
         <v>171</v>
       </c>
       <c r="AA571">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB571">
         <v>8000</v>
@@ -50202,7 +50202,7 @@
         <v>171</v>
       </c>
       <c r="AA572">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB572">
         <v>8000</v>
@@ -50294,7 +50294,7 @@
         <v>171</v>
       </c>
       <c r="AA573">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB573">
         <v>8000</v>
@@ -50377,7 +50377,7 @@
         <v>172</v>
       </c>
       <c r="AA574">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB574">
         <v>8000</v>
@@ -50463,7 +50463,7 @@
         <v>171</v>
       </c>
       <c r="AA575">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB575">
         <v>8000</v>
@@ -50546,7 +50546,7 @@
         <v>172</v>
       </c>
       <c r="AA576">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB576">
         <v>8000</v>
@@ -50629,7 +50629,7 @@
         <v>172</v>
       </c>
       <c r="AA577">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB577">
         <v>8000</v>
@@ -50712,7 +50712,7 @@
         <v>172</v>
       </c>
       <c r="AA578">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB578">
         <v>8000</v>
@@ -50795,7 +50795,7 @@
         <v>172</v>
       </c>
       <c r="AA579">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB579">
         <v>8000</v>
@@ -50884,7 +50884,7 @@
         <v>172</v>
       </c>
       <c r="AA580">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB580">
         <v>8000</v>
@@ -50976,7 +50976,7 @@
         <v>171</v>
       </c>
       <c r="AA581">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB581">
         <v>8000</v>
@@ -51068,7 +51068,7 @@
         <v>171</v>
       </c>
       <c r="AA582">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB582">
         <v>8000</v>
@@ -51151,7 +51151,7 @@
         <v>172</v>
       </c>
       <c r="AA583">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB583">
         <v>8000</v>
@@ -51237,7 +51237,7 @@
         <v>171</v>
       </c>
       <c r="AA584">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB584">
         <v>8000</v>
@@ -51323,7 +51323,7 @@
         <v>171</v>
       </c>
       <c r="AA585">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB585">
         <v>8000</v>
@@ -51409,7 +51409,7 @@
         <v>171</v>
       </c>
       <c r="AA586">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB586">
         <v>8000</v>
@@ -51492,7 +51492,7 @@
         <v>171</v>
       </c>
       <c r="AA587">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB587">
         <v>8000</v>
@@ -51575,7 +51575,7 @@
         <v>171</v>
       </c>
       <c r="AA588">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB588">
         <v>8000</v>
@@ -51661,7 +51661,7 @@
         <v>171</v>
       </c>
       <c r="AA589">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB589">
         <v>8000</v>
@@ -51747,7 +51747,7 @@
         <v>171</v>
       </c>
       <c r="AA590">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB590">
         <v>8000</v>
@@ -51836,7 +51836,7 @@
         <v>172</v>
       </c>
       <c r="AA591">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB591">
         <v>8000</v>
@@ -51928,7 +51928,7 @@
         <v>171</v>
       </c>
       <c r="AA592">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB592">
         <v>8000</v>
@@ -52020,7 +52020,7 @@
         <v>171</v>
       </c>
       <c r="AA593">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB593">
         <v>8000</v>
@@ -52106,7 +52106,7 @@
         <v>171</v>
       </c>
       <c r="AA594">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB594">
         <v>8000</v>
@@ -52192,7 +52192,7 @@
         <v>171</v>
       </c>
       <c r="AA595">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB595">
         <v>8000</v>
@@ -52278,7 +52278,7 @@
         <v>171</v>
       </c>
       <c r="AA596">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB596">
         <v>8000</v>
@@ -52364,7 +52364,7 @@
         <v>171</v>
       </c>
       <c r="AA597">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB597">
         <v>8000</v>
@@ -52456,7 +52456,7 @@
         <v>171</v>
       </c>
       <c r="AA598">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB598">
         <v>8000</v>
@@ -52548,7 +52548,7 @@
         <v>171</v>
       </c>
       <c r="AA599">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB599">
         <v>8000</v>
@@ -52640,7 +52640,7 @@
         <v>171</v>
       </c>
       <c r="AA600">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB600">
         <v>8000</v>
@@ -52726,7 +52726,7 @@
         <v>171</v>
       </c>
       <c r="AA601">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB601">
         <v>8000</v>
@@ -52809,7 +52809,7 @@
         <v>171</v>
       </c>
       <c r="AA602">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB602">
         <v>8000</v>
@@ -52901,7 +52901,7 @@
         <v>171</v>
       </c>
       <c r="AA603">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB603">
         <v>8000</v>
